--- a/SCRUM/Documentação de Log das reuniões.xlsx
+++ b/SCRUM/Documentação de Log das reuniões.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samuc\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43A44EA-6308-4C7A-AFB4-CB14169BD20D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339C701E-646F-493B-AAD0-A9AE57765514}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>Tema</t>
   </si>
@@ -79,14 +79,69 @@
   <si>
     <t>Samuel Arcanjo
 Leonardo Soares</t>
+  </si>
+  <si>
+    <t>Alinhamento de dúvidas para a consultoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisão dos itens questionados na mentoria </t>
+  </si>
+  <si>
+    <t>Construção da apresentação para o Pitch</t>
+  </si>
+  <si>
+    <t>01h30</t>
+  </si>
+  <si>
+    <t>Ensaio e construção da apresentação para o Pitch</t>
+  </si>
+  <si>
+    <t>01h00</t>
+  </si>
+  <si>
+    <t>Ensaio para a apresentação do Pitch</t>
+  </si>
+  <si>
+    <t>Apresentação do Pitch</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Observação:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Boa parte das nossas interações foram realizadas via WhatsApp, sempre discutindo pontos importantes e entendendo o status do trabalho de cada um</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -108,7 +163,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -234,21 +289,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -265,6 +348,31 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,118 +653,235 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="9">
         <v>44285</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="5">
         <v>44286</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="5">
         <v>44292</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="5">
         <v>44293</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="5">
         <v>44299</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="5">
         <v>44301</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="16">
+        <v>44306</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="16">
+        <v>44320</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="16">
+        <v>44322</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="16">
+        <v>44322</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="5">
+        <v>44331</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5">
+        <v>44334</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="14">
+        <v>44336</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="5">
+        <v>44337</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -664,5 +889,6 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>